--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,57 +444,107 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Momentum 20D</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Momentum 60D</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Fuerza relativa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Volumen relativo</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ATR %</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Entrada min</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Entrada max</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Stop loss</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Distancia MA20 %</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Distancia Max20 %</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Confirmacion</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Mercado</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>Riesgo</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Hot Score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Senal</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Razones</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Alertas</t>
         </is>
       </c>
     </row>
@@ -513,55 +563,93 @@
         <v>216.6</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" t="n">
         <v>6.7</v>
       </c>
       <c r="F2" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.31</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>12.22</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>5.64</v>
       </c>
-      <c r="I2" t="n">
-        <v>211.71</v>
-      </c>
-      <c r="J2" t="n">
-        <v>219.65</v>
-      </c>
-      <c r="K2" t="n">
-        <v>198.27</v>
-      </c>
       <c r="L2" t="n">
-        <v>247.14</v>
+        <v>212.32</v>
       </c>
       <c r="M2" t="n">
+        <v>218.43</v>
+      </c>
+      <c r="N2" t="n">
+        <v>200.11</v>
+      </c>
+      <c r="O2" t="n">
+        <v>243.48</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q2" t="n">
         <v>61</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>🔥🔥🔥</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; Momentum 5D extendido; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,2027 +658,3317 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>219.44</v>
+        <v>428.43</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>10.56</v>
+        <v>2.86</v>
       </c>
       <c r="F3" t="n">
-        <v>1.03</v>
+        <v>12.82</v>
       </c>
       <c r="G3" t="n">
-        <v>7.7</v>
+        <v>29.64</v>
       </c>
       <c r="H3" t="n">
-        <v>3.51</v>
+        <v>-2.71</v>
       </c>
       <c r="I3" t="n">
-        <v>216.36</v>
+        <v>0.83</v>
       </c>
       <c r="J3" t="n">
-        <v>221.36</v>
+        <v>15.4</v>
       </c>
       <c r="K3" t="n">
-        <v>207.9</v>
+        <v>3.59</v>
       </c>
       <c r="L3" t="n">
-        <v>238.68</v>
+        <v>423.04</v>
       </c>
       <c r="M3" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+        <v>430.74</v>
+      </c>
+      <c r="N3" t="n">
+        <v>407.64</v>
+      </c>
+      <c r="O3" t="n">
+        <v>462.31</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>MACD sin confirmar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>428.43</v>
+        <v>9.48</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="F4" t="n">
-        <v>0.83</v>
+        <v>11.92</v>
       </c>
       <c r="G4" t="n">
-        <v>15.4</v>
+        <v>-8.67</v>
       </c>
       <c r="H4" t="n">
-        <v>3.59</v>
+        <v>-3.61</v>
       </c>
       <c r="I4" t="n">
-        <v>422.27</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="n">
-        <v>432.28</v>
+        <v>0.43</v>
       </c>
       <c r="K4" t="n">
-        <v>405.33</v>
+        <v>4.57</v>
       </c>
       <c r="L4" t="n">
-        <v>466.93</v>
+        <v>9.33</v>
       </c>
       <c r="M4" t="n">
-        <v>60.96</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1845.19</v>
+        <v>54.93</v>
       </c>
       <c r="D5" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E5" t="n">
-        <v>7.7</v>
+        <v>-1.26</v>
       </c>
       <c r="F5" t="n">
-        <v>1.16</v>
+        <v>5.8</v>
       </c>
       <c r="G5" t="n">
-        <v>83.20999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.51</v>
+        <v>-9.73</v>
       </c>
       <c r="I5" t="n">
-        <v>1811.9</v>
+        <v>0.68</v>
       </c>
       <c r="J5" t="n">
-        <v>1865.99</v>
+        <v>1.69</v>
       </c>
       <c r="K5" t="n">
-        <v>1720.37</v>
+        <v>3.08</v>
       </c>
       <c r="L5" t="n">
-        <v>2053.23</v>
+        <v>54.34</v>
       </c>
       <c r="M5" t="n">
-        <v>54.45</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+        <v>55.18</v>
+      </c>
+      <c r="N5" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="O5" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-3.97</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.48</v>
+        <v>212.65</v>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" t="n">
-        <v>2.82</v>
+        <v>4.62</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>34.95</v>
       </c>
       <c r="G6" t="n">
-        <v>0.43</v>
+        <v>74.03</v>
       </c>
       <c r="H6" t="n">
-        <v>4.57</v>
+        <v>19.42</v>
       </c>
       <c r="I6" t="n">
-        <v>9.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>9.59</v>
+        <v>18.49</v>
       </c>
       <c r="K6" t="n">
-        <v>8.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>10.56</v>
+        <v>206.18</v>
       </c>
       <c r="M6" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+        <v>215.42</v>
+      </c>
+      <c r="N6" t="n">
+        <v>187.69</v>
+      </c>
+      <c r="O6" t="n">
+        <v>253.33</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>60.64</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-11.21</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>🔥🔥</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>404.54</v>
+        <v>1845.19</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.73</v>
+        <v>7.7</v>
       </c>
       <c r="F7" t="n">
-        <v>0.98</v>
+        <v>4.32</v>
       </c>
       <c r="G7" t="n">
-        <v>15.67</v>
+        <v>27.35</v>
       </c>
       <c r="H7" t="n">
-        <v>3.87</v>
+        <v>-11.21</v>
       </c>
       <c r="I7" t="n">
-        <v>398.27</v>
+        <v>1.16</v>
       </c>
       <c r="J7" t="n">
-        <v>408.46</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>381.03</v>
+        <v>4.51</v>
       </c>
       <c r="L7" t="n">
-        <v>443.72</v>
+        <v>1816.06</v>
       </c>
       <c r="M7" t="n">
-        <v>65.77</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+        <v>1857.67</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1732.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2028.26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>MACD sin confirmar; Momentum 5D extendido; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.93</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.26</v>
+        <v>-10.77</v>
       </c>
       <c r="F8" t="n">
-        <v>0.68</v>
+        <v>23.54</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>13.27</v>
       </c>
       <c r="H8" t="n">
-        <v>3.08</v>
+        <v>8.01</v>
       </c>
       <c r="I8" t="n">
-        <v>54.25</v>
+        <v>0.97</v>
       </c>
       <c r="J8" t="n">
-        <v>55.35</v>
+        <v>0.65</v>
       </c>
       <c r="K8" t="n">
-        <v>52.39</v>
+        <v>7.65</v>
       </c>
       <c r="L8" t="n">
-        <v>59.16</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>58.59</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="O8" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-15.88</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; Momentum negativo; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>268.99</v>
+        <v>404.54</v>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.12</v>
+        <v>0.73</v>
       </c>
       <c r="F9" t="n">
-        <v>0.77</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>7.23</v>
+        <v>10.21</v>
       </c>
       <c r="H9" t="n">
-        <v>2.69</v>
+        <v>-6.07</v>
       </c>
       <c r="I9" t="n">
-        <v>266.1</v>
+        <v>0.98</v>
       </c>
       <c r="J9" t="n">
-        <v>270.8</v>
+        <v>15.67</v>
       </c>
       <c r="K9" t="n">
-        <v>258.14</v>
+        <v>3.87</v>
       </c>
       <c r="L9" t="n">
-        <v>287.07</v>
+        <v>399.05</v>
       </c>
       <c r="M9" t="n">
-        <v>72.06</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>406.89</v>
+      </c>
+      <c r="N9" t="n">
+        <v>383.38</v>
+      </c>
+      <c r="O9" t="n">
+        <v>439.02</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-3.68</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>RSI algo alto; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.449999999999999</v>
+        <v>80.78</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.77</v>
+        <v>5.53</v>
       </c>
       <c r="F10" t="n">
-        <v>0.97</v>
+        <v>12.71</v>
       </c>
       <c r="G10" t="n">
-        <v>0.65</v>
+        <v>13.58</v>
       </c>
       <c r="H10" t="n">
-        <v>7.65</v>
+        <v>-2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>8.19</v>
+        <v>0.74</v>
       </c>
       <c r="J10" t="n">
-        <v>8.609999999999999</v>
+        <v>4.22</v>
       </c>
       <c r="K10" t="n">
-        <v>7.48</v>
+        <v>5.23</v>
       </c>
       <c r="L10" t="n">
-        <v>10.07</v>
+        <v>79.3</v>
       </c>
       <c r="M10" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>81.41</v>
+      </c>
+      <c r="N10" t="n">
+        <v>75.08</v>
+      </c>
+      <c r="O10" t="n">
+        <v>90.06999999999999</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-13.44</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.78</v>
+        <v>117.35</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>5.53</v>
+        <v>46.12</v>
       </c>
       <c r="F11" t="n">
-        <v>0.74</v>
+        <v>66.17</v>
       </c>
       <c r="G11" t="n">
-        <v>4.22</v>
+        <v>77.78</v>
       </c>
       <c r="H11" t="n">
-        <v>5.23</v>
+        <v>50.64</v>
       </c>
       <c r="I11" t="n">
-        <v>79.09</v>
+        <v>2.02</v>
       </c>
       <c r="J11" t="n">
-        <v>81.84</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>74.45</v>
+        <v>7.36</v>
       </c>
       <c r="L11" t="n">
-        <v>91.33</v>
+        <v>114.33</v>
       </c>
       <c r="M11" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+        <v>118.65</v>
+      </c>
+      <c r="N11" t="n">
+        <v>105.69</v>
+      </c>
+      <c r="O11" t="n">
+        <v>136.36</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-5.32</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>149.68</v>
+        <v>388.64</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.61</v>
+        <v>1.41</v>
       </c>
       <c r="F12" t="n">
-        <v>0.82</v>
+        <v>20.95</v>
       </c>
       <c r="G12" t="n">
-        <v>4.05</v>
+        <v>25.86</v>
       </c>
       <c r="H12" t="n">
-        <v>2.71</v>
+        <v>5.42</v>
       </c>
       <c r="I12" t="n">
-        <v>148.06</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
-        <v>150.69</v>
+        <v>10.65</v>
       </c>
       <c r="K12" t="n">
-        <v>143.61</v>
+        <v>2.74</v>
       </c>
       <c r="L12" t="n">
-        <v>159.8</v>
+        <v>384.91</v>
       </c>
       <c r="M12" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+        <v>390.24</v>
+      </c>
+      <c r="N12" t="n">
+        <v>374.26</v>
+      </c>
+      <c r="O12" t="n">
+        <v>412.07</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>412.66</v>
+        <v>713.29</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.23</v>
+        <v>6.01</v>
       </c>
       <c r="F13" t="n">
-        <v>0.96</v>
+        <v>15.53</v>
       </c>
       <c r="G13" t="n">
-        <v>11.8</v>
+        <v>18.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>407.94</v>
+        <v>0.88</v>
       </c>
       <c r="J13" t="n">
-        <v>415.61</v>
+        <v>9.84</v>
       </c>
       <c r="K13" t="n">
-        <v>394.96</v>
+        <v>1.38</v>
       </c>
       <c r="L13" t="n">
-        <v>442.16</v>
+        <v>709.84</v>
       </c>
       <c r="M13" t="n">
-        <v>43.47</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>714.77</v>
+      </c>
+      <c r="N13" t="n">
+        <v>700</v>
+      </c>
+      <c r="O13" t="n">
+        <v>734.95</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Momentum 5D extendido; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>184.74</v>
+        <v>795.33</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.92</v>
+        <v>37.97</v>
       </c>
       <c r="F14" t="n">
-        <v>1.16</v>
+        <v>86.45</v>
       </c>
       <c r="G14" t="n">
-        <v>4.61</v>
+        <v>92.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.49</v>
+        <v>70.92</v>
       </c>
       <c r="I14" t="n">
-        <v>182.9</v>
+        <v>1.56</v>
       </c>
       <c r="J14" t="n">
-        <v>185.89</v>
+        <v>45.86</v>
       </c>
       <c r="K14" t="n">
-        <v>177.83</v>
+        <v>5.77</v>
       </c>
       <c r="L14" t="n">
-        <v>196.26</v>
+        <v>779.28</v>
       </c>
       <c r="M14" t="n">
-        <v>48.05</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>802.21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>733.41</v>
+      </c>
+      <c r="O14" t="n">
+        <v>896.23</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="R14" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.14</v>
+        <v>219.44</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.51</v>
+        <v>10.56</v>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>15.92</v>
       </c>
       <c r="G15" t="n">
-        <v>1.85</v>
+        <v>17.39</v>
       </c>
       <c r="H15" t="n">
-        <v>3.36</v>
+        <v>0.39</v>
       </c>
       <c r="I15" t="n">
-        <v>54.4</v>
+        <v>1.03</v>
       </c>
       <c r="J15" t="n">
-        <v>55.6</v>
+        <v>7.7</v>
       </c>
       <c r="K15" t="n">
-        <v>52.36</v>
+        <v>3.51</v>
       </c>
       <c r="L15" t="n">
-        <v>59.76</v>
+        <v>216.75</v>
       </c>
       <c r="M15" t="n">
-        <v>46.84</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>220.59</v>
+      </c>
+      <c r="N15" t="n">
+        <v>209.05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>236.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Subida muy extendida 5D; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>598.86</v>
+        <v>443.62</v>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.89</v>
+        <v>13.35</v>
       </c>
       <c r="F16" t="n">
-        <v>0.92</v>
+        <v>12.1</v>
       </c>
       <c r="G16" t="n">
-        <v>18.32</v>
+        <v>35.26</v>
       </c>
       <c r="H16" t="n">
-        <v>3.06</v>
+        <v>-3.43</v>
       </c>
       <c r="I16" t="n">
-        <v>591.53</v>
+        <v>1.18</v>
       </c>
       <c r="J16" t="n">
-        <v>603.4400000000001</v>
+        <v>17.89</v>
       </c>
       <c r="K16" t="n">
-        <v>571.38</v>
+        <v>4.03</v>
       </c>
       <c r="L16" t="n">
-        <v>644.67</v>
+        <v>437.36</v>
       </c>
       <c r="M16" t="n">
-        <v>26.31</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>446.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>419.47</v>
+      </c>
+      <c r="O16" t="n">
+        <v>482.98</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="R16" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Subida muy extendida 5D; Débil vs QQQ; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.26</v>
+        <v>1565.81</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>0.37</v>
+        <v>12.96</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82</v>
+        <v>11.54</v>
       </c>
       <c r="H17" t="n">
-        <v>5.02</v>
+        <v>-10.93</v>
       </c>
       <c r="I17" t="n">
-        <v>15.93</v>
+        <v>1.16</v>
       </c>
       <c r="J17" t="n">
-        <v>16.46</v>
+        <v>61.22</v>
       </c>
       <c r="K17" t="n">
-        <v>15.04</v>
+        <v>3.91</v>
       </c>
       <c r="L17" t="n">
-        <v>18.3</v>
+        <v>1544.38</v>
       </c>
       <c r="M17" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>1574.99</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1483.16</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1700.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>60.07</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Subida muy extendida 5D; Débil vs QQQ; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>45.07</v>
+        <v>292.68</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="E18" t="n">
-        <v>-10.56</v>
+        <v>5.73</v>
       </c>
       <c r="F18" t="n">
-        <v>1.12</v>
+        <v>12.92</v>
       </c>
       <c r="G18" t="n">
-        <v>1.56</v>
+        <v>11.83</v>
       </c>
       <c r="H18" t="n">
-        <v>3.46</v>
+        <v>-2.61</v>
       </c>
       <c r="I18" t="n">
-        <v>44.45</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
-        <v>45.46</v>
+        <v>6.64</v>
       </c>
       <c r="K18" t="n">
-        <v>42.73</v>
+        <v>2.27</v>
       </c>
       <c r="L18" t="n">
-        <v>48.97</v>
+        <v>290.36</v>
       </c>
       <c r="M18" t="n">
-        <v>23.95</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>293.68</v>
+      </c>
+      <c r="N18" t="n">
+        <v>283.72</v>
+      </c>
+      <c r="O18" t="n">
+        <v>307.28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>136.89</v>
+        <v>296.05</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.26</v>
+        <v>14.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.89</v>
+        <v>10.75</v>
       </c>
       <c r="G19" t="n">
-        <v>6.24</v>
+        <v>28.15</v>
       </c>
       <c r="H19" t="n">
-        <v>4.56</v>
+        <v>-4.78</v>
       </c>
       <c r="I19" t="n">
-        <v>134.39</v>
+        <v>0.86</v>
       </c>
       <c r="J19" t="n">
-        <v>138.45</v>
+        <v>13.7</v>
       </c>
       <c r="K19" t="n">
-        <v>127.53</v>
+        <v>4.63</v>
       </c>
       <c r="L19" t="n">
-        <v>152.49</v>
+        <v>291.25</v>
       </c>
       <c r="M19" t="n">
-        <v>40.84</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>298.11</v>
+      </c>
+      <c r="N19" t="n">
+        <v>277.55</v>
+      </c>
+      <c r="O19" t="n">
+        <v>326.19</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="R19" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>RSI algo alto; Subida muy extendida 5D; Débil vs QQQ; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.69</v>
+        <v>739.3</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.57</v>
+        <v>2.97</v>
       </c>
       <c r="F20" t="n">
-        <v>0.74</v>
+        <v>7.75</v>
       </c>
       <c r="G20" t="n">
-        <v>1.81</v>
+        <v>8.81</v>
       </c>
       <c r="H20" t="n">
-        <v>6.31</v>
+        <v>-7.78</v>
       </c>
       <c r="I20" t="n">
-        <v>27.97</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="n">
-        <v>29.14</v>
+        <v>6.73</v>
       </c>
       <c r="K20" t="n">
-        <v>25.97</v>
+        <v>0.91</v>
       </c>
       <c r="L20" t="n">
-        <v>33.22</v>
+        <v>736.9400000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>33.95</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>740.3099999999999</v>
+      </c>
+      <c r="N20" t="n">
+        <v>730.21</v>
+      </c>
+      <c r="O20" t="n">
+        <v>754.11</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>117.35</v>
+        <v>56.89</v>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
-        <v>46.12</v>
+        <v>24.35</v>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>91.16</v>
       </c>
       <c r="G21" t="n">
-        <v>8.640000000000001</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>7.36</v>
+        <v>75.63</v>
       </c>
       <c r="I21" t="n">
-        <v>113.89</v>
+        <v>1.47</v>
       </c>
       <c r="J21" t="n">
-        <v>119.51</v>
+        <v>4.3</v>
       </c>
       <c r="K21" t="n">
-        <v>104.39</v>
+        <v>7.56</v>
       </c>
       <c r="L21" t="n">
-        <v>138.95</v>
+        <v>55.38</v>
       </c>
       <c r="M21" t="n">
-        <v>68.15000000000001</v>
-      </c>
-      <c r="N21" t="inlineStr">
+        <v>57.54</v>
+      </c>
+      <c r="N21" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="O21" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>65.56</v>
+      </c>
+      <c r="R21" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>56.89</v>
+        <v>532.76</v>
       </c>
       <c r="D22" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>24.35</v>
+        <v>15.3</v>
       </c>
       <c r="F22" t="n">
-        <v>1.47</v>
+        <v>35.45</v>
       </c>
       <c r="G22" t="n">
-        <v>4.3</v>
+        <v>51.66</v>
       </c>
       <c r="H22" t="n">
-        <v>7.56</v>
+        <v>19.92</v>
       </c>
       <c r="I22" t="n">
-        <v>55.17</v>
+        <v>1.08</v>
       </c>
       <c r="J22" t="n">
-        <v>57.97</v>
+        <v>17.4</v>
       </c>
       <c r="K22" t="n">
-        <v>50.44</v>
+        <v>3.27</v>
       </c>
       <c r="L22" t="n">
-        <v>67.64</v>
+        <v>526.67</v>
       </c>
       <c r="M22" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="N22" t="inlineStr">
+        <v>535.37</v>
+      </c>
+      <c r="N22" t="n">
+        <v>509.27</v>
+      </c>
+      <c r="O22" t="n">
+        <v>571.05</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="R22" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1565.81</v>
+        <v>458.79</v>
       </c>
       <c r="D23" t="n">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>12.96</v>
+        <v>34.33</v>
       </c>
       <c r="F23" t="n">
-        <v>1.16</v>
+        <v>85.87</v>
       </c>
       <c r="G23" t="n">
-        <v>61.22</v>
+        <v>122.78</v>
       </c>
       <c r="H23" t="n">
-        <v>3.91</v>
+        <v>70.34</v>
       </c>
       <c r="I23" t="n">
-        <v>1541.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>1581.12</v>
+        <v>27.39</v>
       </c>
       <c r="K23" t="n">
-        <v>1473.98</v>
+        <v>5.97</v>
       </c>
       <c r="L23" t="n">
-        <v>1718.86</v>
+        <v>449.2</v>
       </c>
       <c r="M23" t="n">
-        <v>60.07</v>
-      </c>
-      <c r="N23" t="inlineStr">
+        <v>462.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>421.82</v>
+      </c>
+      <c r="O23" t="n">
+        <v>519.04</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="R23" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>443.62</v>
+        <v>129.44</v>
       </c>
       <c r="D24" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E24" t="n">
-        <v>13.35</v>
+        <v>35.14</v>
       </c>
       <c r="F24" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="G24" t="n">
+        <v>178.49</v>
+      </c>
+      <c r="H24" t="n">
+        <v>83.06</v>
+      </c>
+      <c r="I24" t="n">
         <v>1.18</v>
       </c>
-      <c r="G24" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="I24" t="n">
-        <v>436.46</v>
-      </c>
       <c r="J24" t="n">
-        <v>448.09</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>416.78</v>
+        <v>6.48</v>
       </c>
       <c r="L24" t="n">
-        <v>488.35</v>
+        <v>126.5</v>
       </c>
       <c r="M24" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="N24" t="inlineStr">
+        <v>130.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>118.12</v>
+      </c>
+      <c r="O24" t="n">
+        <v>147.89</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="R24" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>296.05</v>
+        <v>33.52</v>
       </c>
       <c r="D25" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E25" t="n">
-        <v>14.5</v>
+        <v>20.06</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>29.07</v>
       </c>
       <c r="G25" t="n">
-        <v>13.7</v>
+        <v>10.15</v>
       </c>
       <c r="H25" t="n">
-        <v>4.63</v>
+        <v>13.54</v>
       </c>
       <c r="I25" t="n">
-        <v>290.57</v>
+        <v>1.02</v>
       </c>
       <c r="J25" t="n">
-        <v>299.48</v>
+        <v>2.34</v>
       </c>
       <c r="K25" t="n">
-        <v>275.5</v>
+        <v>6.98</v>
       </c>
       <c r="L25" t="n">
-        <v>330.3</v>
+        <v>32.7</v>
       </c>
       <c r="M25" t="n">
-        <v>66.63</v>
-      </c>
-      <c r="N25" t="inlineStr">
+        <v>33.87</v>
+      </c>
+      <c r="N25" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="O25" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="R25" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>292.68</v>
+        <v>445</v>
       </c>
       <c r="D26" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
-        <v>5.73</v>
+        <v>13.37</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8</v>
+        <v>26.27</v>
       </c>
       <c r="G26" t="n">
-        <v>6.64</v>
+        <v>6.7</v>
       </c>
       <c r="H26" t="n">
-        <v>2.27</v>
+        <v>10.74</v>
       </c>
       <c r="I26" t="n">
-        <v>290.02</v>
+        <v>1.17</v>
       </c>
       <c r="J26" t="n">
-        <v>294.34</v>
+        <v>15.49</v>
       </c>
       <c r="K26" t="n">
-        <v>282.72</v>
+        <v>3.48</v>
       </c>
       <c r="L26" t="n">
-        <v>309.27</v>
+        <v>439.58</v>
       </c>
       <c r="M26" t="n">
-        <v>78.04000000000001</v>
-      </c>
-      <c r="N26" t="inlineStr">
+        <v>447.32</v>
+      </c>
+      <c r="N26" t="n">
+        <v>424.09</v>
+      </c>
+      <c r="O26" t="n">
+        <v>479.07</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>78.11</v>
+      </c>
+      <c r="R26" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>739.3</v>
+        <v>268.99</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E27" t="n">
-        <v>2.97</v>
+        <v>-1.12</v>
       </c>
       <c r="F27" t="n">
-        <v>0.85</v>
+        <v>12.13</v>
       </c>
       <c r="G27" t="n">
-        <v>6.73</v>
+        <v>34.76</v>
       </c>
       <c r="H27" t="n">
-        <v>0.91</v>
+        <v>-3.4</v>
       </c>
       <c r="I27" t="n">
-        <v>736.61</v>
+        <v>0.77</v>
       </c>
       <c r="J27" t="n">
-        <v>740.98</v>
+        <v>7.23</v>
       </c>
       <c r="K27" t="n">
-        <v>729.2</v>
+        <v>2.69</v>
       </c>
       <c r="L27" t="n">
-        <v>756.13</v>
+        <v>266.46</v>
       </c>
       <c r="M27" t="n">
-        <v>80.52</v>
-      </c>
-      <c r="N27" t="inlineStr">
+        <v>270.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>259.23</v>
+      </c>
+      <c r="O27" t="n">
+        <v>284.9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>713.29</v>
+        <v>237.53</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="E28" t="n">
-        <v>6.01</v>
+        <v>41.07</v>
       </c>
       <c r="F28" t="n">
-        <v>0.88</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>9.84</v>
+        <v>72.64</v>
       </c>
       <c r="H28" t="n">
-        <v>1.38</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>709.35</v>
+        <v>1.73</v>
       </c>
       <c r="J28" t="n">
-        <v>715.75</v>
+        <v>16.45</v>
       </c>
       <c r="K28" t="n">
-        <v>698.52</v>
+        <v>6.93</v>
       </c>
       <c r="L28" t="n">
-        <v>737.9</v>
+        <v>231.77</v>
       </c>
       <c r="M28" t="n">
-        <v>86.72</v>
-      </c>
-      <c r="N28" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="N28" t="n">
+        <v>215.32</v>
+      </c>
+      <c r="O28" t="n">
+        <v>273.72</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="R28" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
         <is>
           <t>VIGILAR</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>212.65</v>
+        <v>149.68</v>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E29" t="n">
-        <v>4.62</v>
+        <v>-2.61</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.94</v>
       </c>
       <c r="G29" t="n">
-        <v>18.49</v>
+        <v>-0.17</v>
       </c>
       <c r="H29" t="n">
-        <v>8.699999999999999</v>
+        <v>-17.47</v>
       </c>
       <c r="I29" t="n">
-        <v>205.25</v>
+        <v>0.82</v>
       </c>
       <c r="J29" t="n">
-        <v>217.27</v>
+        <v>4.05</v>
       </c>
       <c r="K29" t="n">
-        <v>184.91</v>
+        <v>2.71</v>
       </c>
       <c r="L29" t="n">
-        <v>258.88</v>
+        <v>148.26</v>
       </c>
       <c r="M29" t="n">
-        <v>60.64</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>150.29</v>
+      </c>
+      <c r="N29" t="n">
+        <v>144.21</v>
+      </c>
+      <c r="O29" t="n">
+        <v>158.59</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; MACD mejorando</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>532.76</v>
+        <v>184.74</v>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E30" t="n">
-        <v>15.3</v>
+        <v>-3.92</v>
       </c>
       <c r="F30" t="n">
-        <v>1.08</v>
+        <v>-3.67</v>
       </c>
       <c r="G30" t="n">
-        <v>17.4</v>
+        <v>2.27</v>
       </c>
       <c r="H30" t="n">
-        <v>3.27</v>
+        <v>-19.2</v>
       </c>
       <c r="I30" t="n">
-        <v>525.8</v>
+        <v>1.16</v>
       </c>
       <c r="J30" t="n">
-        <v>537.11</v>
+        <v>4.61</v>
       </c>
       <c r="K30" t="n">
-        <v>506.65</v>
+        <v>2.49</v>
       </c>
       <c r="L30" t="n">
-        <v>576.27</v>
+        <v>183.13</v>
       </c>
       <c r="M30" t="n">
-        <v>78.84999999999999</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>185.43</v>
+      </c>
+      <c r="N30" t="n">
+        <v>178.52</v>
+      </c>
+      <c r="O30" t="n">
+        <v>194.88</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; MACD mejorando</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>795.33</v>
+        <v>412.66</v>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>37.97</v>
+        <v>-0.23</v>
       </c>
       <c r="F31" t="n">
-        <v>1.56</v>
+        <v>7.36</v>
       </c>
       <c r="G31" t="n">
-        <v>45.86</v>
+        <v>2.93</v>
       </c>
       <c r="H31" t="n">
-        <v>5.77</v>
+        <v>-8.17</v>
       </c>
       <c r="I31" t="n">
-        <v>776.98</v>
+        <v>0.96</v>
       </c>
       <c r="J31" t="n">
-        <v>806.8</v>
+        <v>11.8</v>
       </c>
       <c r="K31" t="n">
-        <v>726.53</v>
+        <v>2.86</v>
       </c>
       <c r="L31" t="n">
-        <v>909.99</v>
+        <v>408.53</v>
       </c>
       <c r="M31" t="n">
-        <v>89.27</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>414.43</v>
+      </c>
+      <c r="N31" t="n">
+        <v>396.73</v>
+      </c>
+      <c r="O31" t="n">
+        <v>438.62</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>237.53</v>
+        <v>55.14</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="E32" t="n">
-        <v>41.07</v>
+        <v>-8.51</v>
       </c>
       <c r="F32" t="n">
-        <v>1.73</v>
+        <v>-5.03</v>
       </c>
       <c r="G32" t="n">
-        <v>16.45</v>
+        <v>21.79</v>
       </c>
       <c r="H32" t="n">
-        <v>6.93</v>
+        <v>-20.56</v>
       </c>
       <c r="I32" t="n">
-        <v>230.95</v>
+        <v>1.04</v>
       </c>
       <c r="J32" t="n">
-        <v>241.64</v>
+        <v>1.85</v>
       </c>
       <c r="K32" t="n">
-        <v>212.85</v>
+        <v>3.36</v>
       </c>
       <c r="L32" t="n">
-        <v>278.66</v>
+        <v>54.49</v>
       </c>
       <c r="M32" t="n">
-        <v>89.48</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>55.42</v>
+      </c>
+      <c r="N32" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="O32" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Tendencia larga positiva; MACD mejorando</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>388.64</v>
+        <v>16.26</v>
       </c>
       <c r="D33" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="E33" t="n">
-        <v>1.41</v>
+        <v>0.37</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1</v>
+        <v>-4.63</v>
       </c>
       <c r="G33" t="n">
-        <v>10.65</v>
+        <v>-15.75</v>
       </c>
       <c r="H33" t="n">
-        <v>2.74</v>
+        <v>-20.16</v>
       </c>
       <c r="I33" t="n">
-        <v>384.38</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>391.3</v>
+        <v>0.82</v>
       </c>
       <c r="K33" t="n">
-        <v>372.67</v>
+        <v>5.02</v>
       </c>
       <c r="L33" t="n">
-        <v>415.27</v>
+        <v>15.97</v>
       </c>
       <c r="M33" t="n">
-        <v>82.15000000000001</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>16.38</v>
+      </c>
+      <c r="N33" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="O33" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-19.23</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; MA20 sobre MA50; MACD mejorando</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.52</v>
+        <v>136.89</v>
       </c>
       <c r="D34" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
-        <v>20.06</v>
+        <v>-6.26</v>
       </c>
       <c r="F34" t="n">
-        <v>1.02</v>
+        <v>3.41</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34</v>
+        <v>6.01</v>
       </c>
       <c r="H34" t="n">
-        <v>6.98</v>
+        <v>-12.12</v>
       </c>
       <c r="I34" t="n">
-        <v>32.58</v>
+        <v>0.89</v>
       </c>
       <c r="J34" t="n">
-        <v>34.1</v>
+        <v>6.24</v>
       </c>
       <c r="K34" t="n">
-        <v>30.01</v>
+        <v>4.56</v>
       </c>
       <c r="L34" t="n">
-        <v>39.37</v>
+        <v>134.71</v>
       </c>
       <c r="M34" t="n">
-        <v>61.54</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>137.83</v>
+      </c>
+      <c r="N34" t="n">
+        <v>128.47</v>
+      </c>
+      <c r="O34" t="n">
+        <v>150.62</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; MACD mejorando</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Momentum negativo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>445</v>
+        <v>598.86</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="E35" t="n">
-        <v>13.37</v>
+        <v>-1.89</v>
       </c>
       <c r="F35" t="n">
-        <v>1.17</v>
+        <v>-5.62</v>
       </c>
       <c r="G35" t="n">
-        <v>15.49</v>
+        <v>-7.76</v>
       </c>
       <c r="H35" t="n">
-        <v>3.48</v>
+        <v>-21.15</v>
       </c>
       <c r="I35" t="n">
-        <v>438.81</v>
+        <v>0.92</v>
       </c>
       <c r="J35" t="n">
-        <v>448.87</v>
+        <v>18.32</v>
       </c>
       <c r="K35" t="n">
-        <v>421.77</v>
+        <v>3.06</v>
       </c>
       <c r="L35" t="n">
-        <v>483.72</v>
+        <v>592.45</v>
       </c>
       <c r="M35" t="n">
-        <v>78.11</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>601.61</v>
+      </c>
+      <c r="N35" t="n">
+        <v>574.13</v>
+      </c>
+      <c r="O35" t="n">
+        <v>639.17</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-7.45</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>458.79</v>
+        <v>45.07</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="E36" t="n">
-        <v>34.33</v>
+        <v>-10.56</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9399999999999999</v>
+        <v>-5.14</v>
       </c>
       <c r="G36" t="n">
-        <v>27.39</v>
+        <v>15.68</v>
       </c>
       <c r="H36" t="n">
-        <v>5.97</v>
+        <v>-20.67</v>
       </c>
       <c r="I36" t="n">
-        <v>447.83</v>
+        <v>1.12</v>
       </c>
       <c r="J36" t="n">
-        <v>465.64</v>
+        <v>1.56</v>
       </c>
       <c r="K36" t="n">
-        <v>417.71</v>
+        <v>3.46</v>
       </c>
       <c r="L36" t="n">
-        <v>527.26</v>
+        <v>44.52</v>
       </c>
       <c r="M36" t="n">
-        <v>80.33</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>45.3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="O36" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-13.82</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>129.44</v>
+        <v>28.69</v>
       </c>
       <c r="D37" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>35.14</v>
+        <v>-10.57</v>
       </c>
       <c r="F37" t="n">
-        <v>1.18</v>
+        <v>2.25</v>
       </c>
       <c r="G37" t="n">
-        <v>8.390000000000001</v>
+        <v>-4.97</v>
       </c>
       <c r="H37" t="n">
-        <v>6.48</v>
+        <v>-13.28</v>
       </c>
       <c r="I37" t="n">
-        <v>126.08</v>
+        <v>0.74</v>
       </c>
       <c r="J37" t="n">
-        <v>131.54</v>
+        <v>1.81</v>
       </c>
       <c r="K37" t="n">
-        <v>116.86</v>
+        <v>6.31</v>
       </c>
       <c r="L37" t="n">
-        <v>150.41</v>
+        <v>28.06</v>
       </c>
       <c r="M37" t="n">
-        <v>88.95</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+        <v>28.96</v>
+      </c>
+      <c r="N37" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O37" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-10.21</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-19.86</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar</t>
         </is>
       </c>
     </row>
